--- a/src/attributions/attributions_ig_traj_168.xlsx
+++ b/src/attributions/attributions_ig_traj_168.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,160 +999,160 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1345010810828807</v>
+        <v>0.09023966366787366</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2273454682876108</v>
+        <v>0.1339007297530589</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00242929335295269</v>
+        <v>-0.09598993902530467</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.03466512907320284</v>
+        <v>0.0325068088239986</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2285361925391075</v>
+        <v>0.04171167081709169</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004469526511393119</v>
+        <v>-0.03824423324397312</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1057514036729393</v>
+        <v>0.03607430990243433</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01736233589227211</v>
+        <v>-0.1214751166588389</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.04317109139228038</v>
+        <v>0.0225293782394859</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.07605427972340863</v>
+        <v>-0.06783988486613046</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.01085648554341784</v>
+        <v>0.05624364708042372</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.005367920726140095</v>
+        <v>0.007097728836898055</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.04746778189235903</v>
+        <v>0.09747555169997214</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.0298602511210372</v>
+        <v>-0.02507892520392189</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.07191143125891197</v>
+        <v>0.1961518514915786</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.1717595909833013</v>
+        <v>0.2342463894114579</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.08284363933337956</v>
+        <v>-0.01163091263246434</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.01865155208229204</v>
+        <v>0.06205366458362996</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -1161,79 +1161,79 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.04079309510024247</v>
+        <v>-0.08680639512815318</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.066304162275427</v>
+        <v>0.0900345758788907</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.03283340620120182</v>
+        <v>-0.1027643526596617</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
         <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.02284731819459275</v>
+        <v>-0.0547558034057493</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.05095449535107491</v>
+        <v>-0.09072617358500973</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.06139456390466035</v>
+        <v>-0.04153377870553572</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.0224160439022575</v>
+        <v>0.06722944665165499</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.01880520505166924</v>
+        <v>-0.1358885689599742</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.005576734370991781</v>
+        <v>-0.01047618091381738</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
@@ -1242,28 +1242,28 @@
         <v>0</v>
       </c>
       <c r="CD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.03627934320947346</v>
+        <v>-0.1146466004424216</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.04186594810183301</v>
+        <v>-0.05492256282618978</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.0295740607249829</v>
+        <v>-0.007273429496266994</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL2" t="n">
         <v>-0</v>
@@ -1272,25 +1272,25 @@
         <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.02030754756250808</v>
+        <v>-0.1041364122541963</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.02985302072380105</v>
+        <v>0.09506155402934885</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.05606994475932985</v>
+        <v>-0.0346380168135354</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
@@ -1299,52 +1299,52 @@
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.04935248336591598</v>
+        <v>-0.1140861062878038</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.04417562920233499</v>
+        <v>-0.03985796939907164</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.02296453756375039</v>
+        <v>0.02555597603807475</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
         <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.04407648556797538</v>
+        <v>-0.07058439130442479</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.01310168645478456</v>
+        <v>0.02528522235879207</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05915278330528921</v>
+        <v>-0.01393198104289842</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
         <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
         <v>-0</v>
@@ -1353,19 +1353,19 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.01774329046133111</v>
+        <v>-0.03386568349408878</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.03660075961852761</v>
+        <v>0.01100373457841418</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.01146582227784784</v>
+        <v>0.06338557479467734</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
@@ -1377,49 +1377,49 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.04865450827884053</v>
+        <v>0.0005478695969077751</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.005347755318757407</v>
+        <v>0.0694059202445402</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.02853121857332327</v>
+        <v>0.2087850776267335</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE2" t="n">
         <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.04820678582620177</v>
+        <v>-0.09325252014652387</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.08372349045933243</v>
+        <v>0.1999948748204741</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.01623233054878248</v>
+        <v>0.04307138945784188</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL2" t="n">
         <v>0</v>
@@ -1431,19 +1431,19 @@
         <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.04789466871976065</v>
+        <v>-0.07045460516485143</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.03644610419047922</v>
+        <v>0.04229359336637747</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.03649721248365179</v>
+        <v>0.01750538471923689</v>
       </c>
       <c r="ET2" t="n">
         <v>0</v>
@@ -1458,25 +1458,25 @@
         <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.05197321496315279</v>
+        <v>-0.1406141131538835</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.03525713401926399</v>
+        <v>-0.02660187228028429</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.0279484242845618</v>
+        <v>0.01202228444828498</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
         <v>0</v>
@@ -1485,79 +1485,79 @@
         <v>-0</v>
       </c>
       <c r="FG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.01251368300357263</v>
+        <v>-0.1338460652434464</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.02026803619954162</v>
+        <v>-0.02541160329214602</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.001524862824296119</v>
+        <v>0.06350397843572753</v>
       </c>
       <c r="FL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.0005064520923302226</v>
+        <v>-0.06932199341150445</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.0009808121277767718</v>
+        <v>0.2247367054183777</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.0138916870285865</v>
+        <v>-0.08001435516148918</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
         <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.04312959506008182</v>
+        <v>-0.04777214205195777</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.0299007786849073</v>
+        <v>0.004535383220105026</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF2" t="n">
         <v>-0</v>
@@ -1568,37 +1568,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0.04876077110130773</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0.01534525139931348</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.04813445590215116</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0.02462715323496404</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,130 +1607,130 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>-0.005506313524700379</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.01717672066304168</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.0218758453208398</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0</v>
+        <v>0.04723100095428426</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.02228733215792968</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-0.01831123723843138</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>-0.04089970531048649</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0.0291778682662857</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-0.01299188122394383</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0</v>
+        <v>0.04226965560394599</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0.00800357903721141</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>-0.04675691871190799</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0</v>
+        <v>0.06242260040441281</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0.04549087624631821</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0.006085775867775063</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
@@ -1742,40 +1742,40 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0</v>
+        <v>-0.03529498943684372</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>-0.007494542325871021</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.03249903992310575</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0</v>
+        <v>0.06586073326850636</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0.004080710926122809</v>
       </c>
       <c r="BS3" t="n">
         <v>0</v>
@@ -1784,61 +1784,61 @@
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>-0.005296927392255324</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0</v>
+        <v>0.01593254948622829</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0.009872337940771881</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.03454422478574509</v>
       </c>
       <c r="CE3" t="n">
         <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0</v>
+        <v>-0.02974396190330431</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.02186074266052758</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>0.005318421011263669</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
@@ -1847,43 +1847,43 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0</v>
+        <v>-0.08272789923982712</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.03732467953717443</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.03191027520673255</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>-0.03812139512729863</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.0314374034645038</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1892,52 +1892,52 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>-0.004238982111062281</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>-0.05313477050775502</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.006016717435428695</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.01911277246533327</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0</v>
+        <v>-0.02704193242942433</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0.003822123019691176</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
@@ -1946,37 +1946,37 @@
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.002790571064553145</v>
       </c>
       <c r="DX3" t="n">
         <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0</v>
+        <v>0.04308094699296719</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.07329148470590857</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.03159503054418335</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH3" t="n">
         <v>0</v>
@@ -1985,13 +1985,13 @@
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>-0.009405864240237856</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.0119831861820647</v>
       </c>
       <c r="EM3" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.02051638623174549</v>
       </c>
       <c r="EP3" t="n">
         <v>0</v>
@@ -2012,22 +2012,22 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0</v>
+        <v>-0.07075949629784747</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0.01283276226143453</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.04155260792313908</v>
       </c>
       <c r="EY3" t="n">
         <v>0</v>
@@ -2039,49 +2039,49 @@
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0</v>
+        <v>-0.04843127525550123</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.03496974125395826</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.03313490002826699</v>
       </c>
       <c r="FH3" t="n">
         <v>0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0</v>
+        <v>0.03465291262383509</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0.006563619870532774</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.02416719357425679</v>
       </c>
       <c r="FQ3" t="n">
         <v>0</v>
@@ -2090,49 +2090,6877 @@
         <v>0</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0</v>
+        <v>-0.06113979343777934</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.02926767154871138</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
         <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.009710750477994389</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
         <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.04217608154408795</v>
       </c>
       <c r="GF3" t="n">
         <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.4319490946890656</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1396577411406018</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.3570316746354883</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2538268075066806</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.004827927332123014</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.09717474565120979</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.1685367359188457</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.1164730141306596</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-0.09380615921067247</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.1366580686165931</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.1455139155584118</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.1816958103360177</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.07520062877766218</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.004156821163288848</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.2155488977733756</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.3908905114335131</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-0.3225416082356404</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-0.4410444184458641</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.2373335845406943</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.1815640566988945</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-0.1867837599198924</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.02172987551879752</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.1045660639133604</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.1240673306047938</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.06135329951687372</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>-0.0386331961741841</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>-0.1219541106830468</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>-0.2573773707333824</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-0.06129777083132828</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.1810507297472903</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>-0.306934362278054</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.03979477165268149</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.2713245348856079</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>-0.2463444593856826</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>-0.05657490753672796</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0.149905525013459</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>-0.07513373605606063</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>-0.04558707248034287</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0.1611843879153292</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>-0.151950988301143</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>-0.01226492203254822</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.008546501819943925</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>0.1837443454348131</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>-0.1277529552528849</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.1593533498361075</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>-0.1035194772797161</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>-0.09457791910238449</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>0.1350889653418169</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>-0.1469717700830418</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>-0.1998571348546632</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0.2449327440190437</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>-0.2289751266052609</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>-0.1044559079647765</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>0.1596762777159333</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>-0.05666246834881207</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>-0.09187575996671468</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>0.2729150168882057</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0.04207565157335859</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>-0.03414438995355668</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>0.0461961237306356</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>-0.09160564727738563</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>0.1071642378864993</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.3896151253905897</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05890225982844868</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.1908771582649929</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2220082508423457</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.01863044986990919</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.1491827895576141</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.0863426065992861</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.1348133298541829</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.02618214709893321</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0.01784667772164039</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.209836313351146</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.01451694224097063</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.148122760783164</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.1099785602155992</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.07089968219090624</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.4615034817242039</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.1225279896211901</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-0.08330765654477906</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.0350884626594479</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.06146841455755944</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.1465721667489681</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-0.01247149706931173</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.09235637240710486</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.09875650707383818</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.1149824484535984</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.002243305385305163</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>-0.09353314297682778</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-0.1837887770443466</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>-0.05964168157475488</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.1301016091843135</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>-0.1303757699858601</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.08633599357262636</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-0.009968014194335554</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-0.1626929666028039</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>-0.03762067619888508</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.1368038130561224</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0.03850245110347926</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.1793499262207665</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.03911413564798904</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-0.08356083994529917</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>-0.0130043466988754</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.0414661139997895</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0.009656007208351537</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>0.09069660333624394</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0.09308017777366165</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>-0.06908112964857854</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.08194580475648673</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0.05593984795091946</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>-0.1102934867800927</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>-0.09525893541118385</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0.07350095112330209</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>-0.1778663002085887</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>-0.07707041082105195</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.1211545422378253</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>-0.1878067768564899</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.04097617996809625</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.2224683691506054</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>-0.01737431261793794</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>-0.003379152748363384</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0.1669410149558901</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>-0.09778621214479991</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0.07067941542265195</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.4327665036014632</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.05960213053208405</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.2678264799782845</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.3157788638614374</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.02898072355668871</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.2027468044367603</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1069644057881666</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.1385703024237975</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.03362962976882945</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.05625180174353993</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.260182595400243</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.1267504128541096</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1534652290755144</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.1054224908819899</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-0.09497176661642012</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.5222777954167791</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.1409027530658058</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0.1995977779695688</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.06371806801457591</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0.08828500092932828</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>-0.2324484597730503</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-0.0146907352167341</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.08211443783137491</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.04517393560092541</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.1223490267335779</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0.0009127553055775733</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>-0.06435431995530227</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0.2020179260281987</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0.05587182838796809</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.1556900391520405</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0.2482132739606406</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.1374031177870805</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.08158914971801268</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>-0.1881277065572423</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>-0.05268957628616023</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.152865313339873</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0.06059034929064328</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0.05941553815982453</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.01374647169052855</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0.08470052605696637</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>-0.04344962511447749</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.126085750382061</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.02228625394812905</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.1596697922196088</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.1257478569775997</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0.07443428715425464</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>-0.06315497263971176</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0.05966740676743278</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-0.08959243716799904</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>-0.06758867114239693</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0.1439865285737395</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>-0.2082631024677325</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>-0.07841841932020624</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0.1314201631145835</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>-0.25370235070929</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0.08144340206844049</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.2335241355488746</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>-0.03350312019763925</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>-0.008796733144985381</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0.1336381811428423</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>-0.05208006654095459</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.05200129599896613</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.5340436257977584</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1116010307410972</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.02061946699802905</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.118908662128799</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4409127644344682</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.2041090641734286</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.05851909554274766</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.0633687227959831</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.06160569478745891</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.05235646825349604</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.08274871558512378</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.02846892918666222</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.051598942449204</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.3125431169408243</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.1727083327403095</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.01473900825342343</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1647783675199556</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.0583392005053493</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.09944911406009137</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.1346943143594716</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.4108132032623315</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.006586978326525935</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.1653473278652595</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.1445516502582342</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.133856969724293</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.111707493098299</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.07602155429935514</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-0.07064402636949918</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-0.02958571576610897</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.05707777972314394</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.182313309394433</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.004002939907230134</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.1014024779935604</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.001082059562094121</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.009016087195190413</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>-0.04421864232736604</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.183967120355417</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.07388929883321003</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.01269362454356874</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.06065852247639247</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.1688068634771505</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.07628984711024296</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.08409406618642264</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.1206823222135179</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.1735489581310823</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.04987885355794108</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.0274715813357367</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.05448546555459702</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-0.03477193405473357</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>-0.05058169833671786</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.2636006581505823</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>-0.002810203244321643</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.1149179321812341</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.01749329044356634</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0.04339219236821079</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.08015772898240696</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.06318564306538824</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.07074322380332891</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.01896458187223646</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>-0.03552124068435348</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0.100934400989094</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.1152329023842482</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.07389481167208076</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>-0.01621451516753155</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0.05545511889759486</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>-0.05108515081568232</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0.005424855713293991</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.1451221247194502</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0.193051696446453</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.060987557414808</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>-0.008043182796486406</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.02692042352156259</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0.1417643806056811</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.07725193665865417</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>-0.008953531871852809</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.173288298649937</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>-0.1752208756571573</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.2056604080196844</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>-3.492566339990914e-05</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.02571129705059264</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>-0.1586913979300996</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>-0.0888790861291741</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>-0.003030557642252899</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.30956592225856</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01036084130510146</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1435040209615415</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.2075334196501905</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.08596809553700351</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06056711800428739</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.08916871836298497</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.01505523398634346</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.0563505307471709</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.04380669759589225</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.0743569622644705</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0.02017354272131931</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.1022025009360546</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0.1180908184258008</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.09822061194093787</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.2683484414514687</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.01124655641504051</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.02302204646360979</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.08804758165984154</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.2186771462591993</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.1154957142685973</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.05290726982786845</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-0.04200938535816679</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.003946778997318605</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-0.1176780004189607</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0.01093137857012047</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.02447597718212515</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.13329876262247</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.008067206196405264</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>-0.04116785515495565</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.118020207592426</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>-0.1410034112376731</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-0.02243687267510725</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.1246630922160658</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>-0.008439126948974933</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>-0.03674769079848763</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-0.001223795478487699</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.107478144696642</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-0.03549996441900764</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.06473062791211627</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.01118673096310786</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.02728275619929104</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.005089028358445664</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>-0.02548464319731589</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.02516550754034229</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.08409907513899312</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>-0.0177423086361595</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.02023169803248686</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.09319385620661369</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.08387423323249259</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.150500830215152</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.1468858582035797</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.009500381045378254</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>-0.03579254409894344</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.1303062565458542</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-0.06808524344849437</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>-0.05791572196171264</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.1061919887334039</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0.00659444850220786</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>-0.04605192372611724</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.130515650438532</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.05215753058011549</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4146125207704624</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.05207452710402113</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.1790269126989837</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.4897812751699794</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.02611954054621623</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.1077201026749958</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.08348644091783308</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.03729487208213216</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.07029019053597879</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.01426544904261823</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.04519994309211058</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.05513200705446745</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.1189812057696314</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.05064910715452189</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.07933182777694389</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.4014265659622342</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.152434504479038</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.1197799690979786</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.09921984838558168</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-0.009251170599771336</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.0410941194083878</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-0.05517743066198927</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.06516634054425277</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.02185417816043962</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.1570654689290278</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0.02104657625815914</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0.03886893431891503</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>-0.1570383738134778</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>-0.01207096525587374</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.04970884300167105</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>-0.06638936076247952</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.06810614489903058</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.02615483046173043</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-0.1493666420965451</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>-0.008362436643464539</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.05728224203720628</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.007794652542282024</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.00996522180328719</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.08623806646556748</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>-0.09762773578366853</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>-0.05209595927864816</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.08857452112380632</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>-0.06870570319216675</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.02790455680907981</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>-0.0723903590220841</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>-0.09466257787746508</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>-0.0270214566157771</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.01384819013036469</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.08220914299519202</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>0.01000134630600217</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>-0.06439418855653099</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>-0.1660666432769764</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>-0.02787559267825401</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.06176415159839486</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>-0.05121062845512878</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>-0.002955520315658142</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.04756725100075073</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>-0.1338858693816095</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>-0.07176813529414308</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>-0.005154080410205381</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>-0.1097058850811157</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.0375381716589314</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.5149382731298888</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.2760448351347395</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.03285947203287068</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.5886652741603915</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.378868518525178</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.1536346311224946</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.0947041501572275</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.02746328833423306</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.02178324017184599</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.04246912218655872</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.1694871868491387</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.06667299587815725</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.1270046254348038</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.07793390841935197</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.1258650049027836</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.488877726247879</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-0.1550904432348834</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.08739020753733329</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-0.07263881446242926</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0.0992588315640935</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-0.0822951158036045</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>-0.04487358345780825</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.01380299134225591</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.06952022009350413</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.1895723763494251</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>-0.0919026667662149</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>-0.01720944562385496</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>-0.1531865785019369</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.1223931464088589</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>-0.01237468056512737</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>-0.08657866632421461</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.1601811934430927</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.06081607374153204</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>-0.1562192968918456</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0.1307190193109442</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.01620265611443198</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>-0.1109633325514608</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0.08215171766505835</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.007492052622283114</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>-0.09054958118374251</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.08249209807509857</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>-0.07252728848190834</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>-0.07358168103618298</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>-0.01907379462318395</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.02546675801482851</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>-0.1157561551658658</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0.1067575776976637</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.02624964130309788</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.08200473383280397</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0.08034219543200442</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.0418516740465874</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>-0.1836062187819605</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0.1452914228519701</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>-0.02761343834211873</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>-0.0585101171525725</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>-0.1057265279910604</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>-0.01302659597671004</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>-0.1536956729104191</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>-0.02198215415205464</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.1083981993760141</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>-0.1297134265684114</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>0.04571055798988061</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.9154176255340356</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.2952771180719096</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.8210146960521149</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.161822300127267</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.9796835448708368</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.9466126626393371</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.2769772541037757</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.1634675324324047</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.1530207755476072</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.2007406169185788</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.4556709296773129</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0.1809809179378997</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.357332246623919</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.1105079278586931</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.1858024631792063</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.716530802866336</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.2711362897776961</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.6107013642164573</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.5819687448278155</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.2689609360229874</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0.02049538622569079</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.1356244800788722</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.1856584314732913</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.138081535516047</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.6717759998778456</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0.2066270931128476</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>-0.3640407200538752</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0.3235804982403826</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.1642646099514525</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.2099296872523417</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0.3656273692701761</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.3987913114132937</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.1828538613029201</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0.2866392965304727</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.1642145868638853</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.2822667615579754</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>-0.2345592387079171</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0.3778626267774362</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.2633023963166696</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0.09170580695657705</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>-0.1085135878109885</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.1877288249857243</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>-0.2975882033812618</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.06958224986686548</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.05441078486052926</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0.2004448273991978</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.116022166178487</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>-0.06518256046486244</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0.1983197487913107</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0.006200669851622103</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.1785873061320501</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0.3596955428639713</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.09376687730621741</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.2474087535909296</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>-0.2007603589976811</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.1265693348354134</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.2646402280863294</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>-0.1418217932065887</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.3975011866316001</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>-0.1703091867510553</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>-0.01817749321557701</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.07345275855659406</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.4461305712729974</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.1986620095522671</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.01181099634678071</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.4504705668989015</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.2690757329511134</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.05319611388135223</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.07390396228625766</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.05825248555488427</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.01881476674452279</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.009764027054499792</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.1502414545083642</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.01144924257941493</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.1088075246020502</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.06124552354016068</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.09845015623371056</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.3047941533022991</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-0.07950848856990177</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.1318852038334846</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0.005861337058742435</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-0.1051546304923273</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0.01611512253239625</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-0.003149744362867394</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.004925217054181013</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.04210998662296928</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.2154682670337422</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>-0.04338195055731589</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0.02500136902072409</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0.1247219495712694</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.09834728440461291</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>-0.0133724601163946</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0.1024331777876969</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0.1382949193181361</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.03873126281042349</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>-0.1213552857570784</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0.1107492481003431</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>-0.005546055592276195</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0.07312814168706695</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0.04822040261229554</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>-0.0445480601830337</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0.07336638472573317</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>-0.0612509612091002</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>-0.002849066979302629</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>-0.1008983247691735</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0.04576855740015798</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>0.0363914610438491</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0.1048014177554082</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0.09924609789597735</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>0.007229874952478376</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>0.02896946540527011</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0.04087595639908014</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>0.00506994986952817</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0.1394693185391009</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0.1195182165512341</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>-0.01989906592662548</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>-0.03327846927940543</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0.06910947984829478</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>-0.1128259980178284</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>-0.1750365850483613</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0.06186546127645406</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0.1411185388781749</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>-0.1072203876966592</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0.06450276871826796</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
